--- a/entregables/Proyectos_2026-2_resumen.xlsx
+++ b/entregables/Proyectos_2026-2_resumen.xlsx
@@ -1,64 +1,166 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d2f440db51dfc7c7/Documentos/GitHub/Mineria-de-Datos-en-Phyton/entregables/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_1B376543467C3BD86F56B4FF9C1B6216DD652D8C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C9390522-C76D-4C35-AB4B-7317722291F9}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hoja1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="191028" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+  <si>
+    <t>Equipo</t>
+  </si>
+  <si>
+    <t>Empresa 
+(a quien pertenecen los datos)</t>
+  </si>
+  <si>
+    <t>Datos Iniciales
+(cantidad de columnas, cantidad de filas, variable objetivo)</t>
+  </si>
+  <si>
+    <t>Enlace para descarga de los datos</t>
+  </si>
+  <si>
+    <t>MINERÍA DE DATOS</t>
+  </si>
+  <si>
+    <t>VISUALIZACIÓN</t>
+  </si>
+  <si>
+    <t>BODEGA DE DATOS</t>
+  </si>
+  <si>
+    <t>ETL</t>
+  </si>
+  <si>
+    <t>BIG DATA</t>
+  </si>
+  <si>
+    <t>CONCLUSIÓN FINAL</t>
+  </si>
+  <si>
+    <t>Calidad  de datos</t>
+  </si>
+  <si>
+    <t>Preparación de datos</t>
+  </si>
+  <si>
+    <t>Modelos analíticos Python</t>
+  </si>
+  <si>
+    <t>Modelos analíticos Knime</t>
+  </si>
+  <si>
+    <t>Enlace al power BI y una conclusión de los gráficos</t>
+  </si>
+  <si>
+    <t>Hechos</t>
+  </si>
+  <si>
+    <t>Dimensiones</t>
+  </si>
+  <si>
+    <t>Extraccion - Transformacion - Carga</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> (enlaces de los dashboards)</t>
+  </si>
+  <si>
+    <t>Diagnóstico de las dimensiones de calidad</t>
+  </si>
+  <si>
+    <t>Indicar los pasos de preparación implementados y hallazgos</t>
+  </si>
+  <si>
+    <t>(Indicar resultados de modelos predictivos con validación cruzada)</t>
+  </si>
+  <si>
+    <t>(Indicar modelos creados y una conclusion de cada modelo)</t>
+  </si>
+  <si>
+    <t>Nicolás Castrillón, Mateo Roldán, Matías Arango</t>
+  </si>
+  <si>
+    <t>No aplica — dataset histórico público (pasajeros del RMS Titanic), sin empresa propietaria</t>
+  </si>
+  <si>
+    <t>12 columnas originales (7 usadas como predictoras tras la selección de factores), 891 filas, variable objetivo: Survived (1 = sobrevivió, 0 = no sobrevivió)</t>
+  </si>
+  <si>
+    <t>https://github.com/Mateo-R99/Mineria-de-Datos-en-Phyton/blob/main/data/titanic.csv</t>
+  </si>
+  <si>
+    <t>Completitud: Age con 19.8% de nulos (177/891, imputados con la mediana), Embarked con 0.2% de nulos (2/891, imputados con la moda), Cabin con 77% de nulos (687/891, se descartó la columna por no ser confiablemente imputable). Duplicidad: 0 filas duplicadas. Exactitud: sin edades ni tarifas fuera de rango (no se encontraron valores negativos ni edades &gt;100). Conformidad: formatos de las variables consistentes en todo el archivo. Integridad: dataset autocontenido, no requiere cruces con otras fuentes.</t>
+  </si>
+  <si>
+    <t>Se eliminaron PassengerId, Name y Ticket (identificadores sin valor predictivo) y Cabin (77% nula). Imputación de Age (mediana) y Embarked (moda), escalado estandarizado de variables numéricas y codificación dummy de categóricas, todo dentro de un Pipeline de scikit-learn ajustado solo con el conjunto de entrenamiento (evita fuga de información). Selección de factores con correlación punto-biserial, chi-cuadrado + V de Cramér e importancia de Random Forest: Sex (V=0.54) y Pclass (V=0.34) resultaron las variables más asociadas a la supervivencia, seguidas de Fare (r=0.26) y Age (relación no lineal, relevante en el Random Forest pese a correlación lineal débil). Sin redundancia fuerte entre predictoras (correlación máxima entre ellas: 0.41).</t>
+  </si>
+  <si>
+    <t>6 modelos evaluados con validación cruzada estratificada de 5 folds (accuracy / CV, brecha train-test): Árbol de Decisión 0.801 (brecha 0.070), KNN 0.775 (la más baja), Red Neuronal (MLP) 0.808 (brecha 0.060), SVM 0.825 (brecha 0.026, buena generalización), Random Forest 0.822 (mejor ROC-AUC: 0.868, brecha 0.060), XGBoost 0.825 (brecha 0.127, overfitting claro). Se optimizó Random Forest con GridSearchCV (n_estimators=200, max_depth=6, min_samples_leaf=1, max_features='sqrt'): ROC-AUC de validación cruzada subió de 0.868 a 0.871, y en el conjunto de prueba (no usado durante la búsqueda) el accuracy pasó de 0.813 a 0.817 y el ROC-AUC de 0.858 a 0.862, sin aumentar la brecha train-test. Modelo final desplegado con interfaz en Streamlit.</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="5">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b val="1"/>
-      <color rgb="FF000000"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color rgb="FF000000"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="10"/>
-      <sz val="11"/>
-      <u val="single"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b val="1"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="8">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -71,19 +173,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.5999938962981048"/>
+        <fgColor theme="9" tint="0.59999389629810485"/>
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.5999938962981048"/>
+        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.3999755851924192"/>
+        <fgColor theme="4" tint="0.39997558519241921"/>
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
@@ -95,12 +197,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="2" tint="-0.09997863704336681"/>
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -137,19 +239,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -171,35 +260,6 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -231,79 +291,81 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="23">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Hyperlink" xfId="1"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -569,212 +631,142 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col width="14.81640625" customWidth="1" min="1" max="1"/>
-    <col width="45.1796875" customWidth="1" min="2" max="2"/>
-    <col width="57" customWidth="1" min="3" max="3"/>
-    <col width="93.1796875" customWidth="1" min="4" max="5"/>
-    <col width="86" customWidth="1" min="6" max="6"/>
-    <col width="83" customWidth="1" min="7" max="7"/>
-    <col width="89.81640625" customWidth="1" min="8" max="8"/>
-    <col width="159" customWidth="1" min="9" max="9"/>
-    <col width="64.26953125" customWidth="1" min="10" max="10"/>
-    <col width="80.7265625" customWidth="1" min="11" max="11"/>
-    <col width="89" customWidth="1" min="12" max="12"/>
-    <col width="77.453125" customWidth="1" min="13" max="13"/>
-    <col width="81.453125" customWidth="1" min="14" max="14"/>
+    <col min="1" max="1" width="14.77734375" customWidth="1"/>
+    <col min="2" max="2" width="45.21875" customWidth="1"/>
+    <col min="3" max="3" width="57" customWidth="1"/>
+    <col min="4" max="5" width="93.21875" customWidth="1"/>
+    <col min="6" max="6" width="86" customWidth="1"/>
+    <col min="7" max="7" width="83" customWidth="1"/>
+    <col min="8" max="8" width="89.77734375" customWidth="1"/>
+    <col min="9" max="9" width="159" customWidth="1"/>
+    <col min="10" max="10" width="64.21875" customWidth="1"/>
+    <col min="11" max="11" width="80.77734375" customWidth="1"/>
+    <col min="12" max="12" width="89" customWidth="1"/>
+    <col min="13" max="13" width="77.44140625" customWidth="1"/>
+    <col min="14" max="14" width="81.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1">
-      <c r="A1" s="14" t="inlineStr">
-        <is>
-          <t>Equipo</t>
-        </is>
-      </c>
-      <c r="B1" s="15" t="inlineStr">
-        <is>
-          <t>Empresa 
-(a quien pertenecen los datos)</t>
-        </is>
-      </c>
-      <c r="C1" s="15" t="inlineStr">
-        <is>
-          <t>Datos Iniciales
-(cantidad de columnas, cantidad de filas, variable objetivo)</t>
-        </is>
-      </c>
-      <c r="D1" s="15" t="inlineStr">
-        <is>
-          <t>Enlace para descarga de los datos</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>MINERÍA DE DATOS</t>
-        </is>
-      </c>
-      <c r="F1" s="20" t="n"/>
-      <c r="G1" s="20" t="n"/>
-      <c r="H1" s="21" t="n"/>
-      <c r="I1" s="9" t="inlineStr">
-        <is>
-          <t>VISUALIZACIÓN</t>
-        </is>
-      </c>
-      <c r="J1" s="10" t="inlineStr">
-        <is>
-          <t>BODEGA DE DATOS</t>
-        </is>
-      </c>
-      <c r="K1" s="21" t="n"/>
-      <c r="L1" s="2" t="inlineStr">
-        <is>
-          <t>ETL</t>
-        </is>
-      </c>
-      <c r="M1" s="3" t="inlineStr">
-        <is>
-          <t>BIG DATA</t>
-        </is>
-      </c>
-      <c r="N1" s="4" t="inlineStr">
-        <is>
-          <t>CONCLUSIÓN FINAL</t>
-        </is>
+    <row r="1" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="17"/>
+      <c r="L1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="22" t="n"/>
-      <c r="B2" s="22" t="n"/>
-      <c r="C2" s="22" t="n"/>
-      <c r="D2" s="22" t="n"/>
-      <c r="E2" s="5" t="inlineStr">
-        <is>
-          <t>Calidad  de datos</t>
-        </is>
-      </c>
-      <c r="F2" s="5" t="inlineStr">
-        <is>
-          <t>Preparación de datos</t>
-        </is>
-      </c>
-      <c r="G2" s="1" t="inlineStr">
-        <is>
-          <t>Modelos analíticos Python</t>
-        </is>
-      </c>
-      <c r="H2" s="1" t="inlineStr">
-        <is>
-          <t>Modelos analíticos Knime</t>
-        </is>
-      </c>
-      <c r="I2" s="11" t="inlineStr">
-        <is>
-          <t>Enlace al power BI y una conclusión de los gráficos</t>
-        </is>
-      </c>
-      <c r="J2" s="10" t="inlineStr">
-        <is>
-          <t>Hechos</t>
-        </is>
-      </c>
-      <c r="K2" s="10" t="inlineStr">
-        <is>
-          <t>Dimensiones</t>
-        </is>
-      </c>
-      <c r="L2" s="16" t="inlineStr">
-        <is>
-          <t>Extraccion - Transformacion - Carga</t>
-        </is>
-      </c>
-      <c r="M2" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> (enlaces de los dashboards)</t>
-        </is>
-      </c>
-      <c r="N2" s="13" t="n"/>
+    <row r="2" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="12"/>
+      <c r="B2" s="12"/>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2" s="21" t="s">
+        <v>14</v>
+      </c>
+      <c r="J2" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="K2" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="L2" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="M2" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="N2" s="15"/>
     </row>
-    <row r="3" ht="29.15" customHeight="1">
-      <c r="A3" s="23" t="n"/>
-      <c r="B3" s="23" t="n"/>
-      <c r="C3" s="23" t="n"/>
-      <c r="D3" s="23" t="n"/>
-      <c r="E3" s="8" t="inlineStr">
-        <is>
-          <t>Diagnóstico de las dimensiones de calidad</t>
-        </is>
-      </c>
-      <c r="F3" s="8" t="inlineStr">
-        <is>
-          <t>Indicar los pasos de preparación implementados y hallazgos</t>
-        </is>
-      </c>
-      <c r="G3" s="6" t="inlineStr">
-        <is>
-          <t>(Indicar resultados de modelos predictivos con validación cruzada)</t>
-        </is>
-      </c>
-      <c r="H3" s="7" t="inlineStr">
-        <is>
-          <t>(Indicar modelos creados y una conclusion de cada modelo)</t>
-        </is>
-      </c>
-      <c r="I3" s="23" t="n"/>
-      <c r="J3" s="23" t="n"/>
-      <c r="K3" s="23" t="n"/>
-      <c r="L3" s="23" t="n"/>
-      <c r="M3" s="23" t="n"/>
-      <c r="N3" s="23" t="n"/>
+    <row r="3" spans="1:14" ht="29.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="13"/>
+      <c r="B3" s="13"/>
+      <c r="C3" s="13"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I3" s="13"/>
+      <c r="J3" s="13"/>
+      <c r="K3" s="13"/>
+      <c r="L3" s="13"/>
+      <c r="M3" s="13"/>
+      <c r="N3" s="13"/>
     </row>
-    <row r="4" ht="220" customHeight="1">
-      <c r="A4" s="24" t="inlineStr">
-        <is>
-          <t>Nicolás Castrillón, Mateo Roldán, Matías Arango</t>
-        </is>
-      </c>
-      <c r="B4" s="24" t="inlineStr">
-        <is>
-          <t>No aplica — dataset histórico público (pasajeros del RMS Titanic), sin empresa propietaria</t>
-        </is>
-      </c>
-      <c r="C4" s="24" t="inlineStr">
-        <is>
-          <t>12 columnas originales (7 usadas como predictoras tras la selección de factores), 891 filas, variable objetivo: Survived (1 = sobrevivió, 0 = no sobrevivió)</t>
-        </is>
-      </c>
-      <c r="D4" s="24" t="inlineStr">
-        <is>
-          <t>https://github.com/Mateo-R99/Mineria-de-Datos-en-Phyton/blob/main/data/titanic.csv</t>
-        </is>
-      </c>
-      <c r="E4" s="24" t="inlineStr">
-        <is>
-          <t>Completitud: Age con 19.8% de nulos (177/891, imputados con la mediana), Embarked con 0.2% de nulos (2/891, imputados con la moda), Cabin con 77% de nulos (687/891, se descartó la columna por no ser confiablemente imputable). Duplicidad: 0 filas duplicadas. Exactitud: sin edades ni tarifas fuera de rango (no se encontraron valores negativos ni edades &gt;100). Conformidad: formatos de las variables consistentes en todo el archivo. Integridad: dataset autocontenido, no requiere cruces con otras fuentes.</t>
-        </is>
-      </c>
-      <c r="F4" s="24" t="inlineStr">
-        <is>
-          <t>Se eliminaron PassengerId, Name y Ticket (identificadores sin valor predictivo) y Cabin (77% nula). Imputación de Age (mediana) y Embarked (moda), escalado estandarizado de variables numéricas y codificación dummy de categóricas, todo dentro de un Pipeline de scikit-learn ajustado solo con el conjunto de entrenamiento (evita fuga de información). Selección de factores con correlación punto-biserial, chi-cuadrado + V de Cramér e importancia de Random Forest: Sex (V=0.54) y Pclass (V=0.34) resultaron las variables más asociadas a la supervivencia, seguidas de Fare (r=0.26) y Age (relación no lineal, relevante en el Random Forest pese a correlación lineal débil). Sin redundancia fuerte entre predictoras (correlación máxima entre ellas: 0.41).</t>
-        </is>
-      </c>
-      <c r="G4" s="24" t="inlineStr">
-        <is>
-          <t>6 modelos evaluados con validación cruzada estratificada de 5 folds (accuracy / CV, brecha train-test): Árbol de Decisión 0.801 (brecha 0.070), KNN 0.775 (la más baja), Red Neuronal (MLP) 0.808 (brecha 0.060), SVM 0.825 (brecha 0.026, buena generalización), Random Forest 0.822 (mejor ROC-AUC: 0.868, brecha 0.060), XGBoost 0.825 (brecha 0.127, overfitting claro). Se optimizó Random Forest con GridSearchCV (n_estimators=200, max_depth=6, min_samples_leaf=1, max_features='sqrt'): ROC-AUC de validación cruzada subió de 0.868 a 0.871, y en el conjunto de prueba (no usado durante la búsqueda) el accuracy pasó de 0.813 a 0.817 y el ROC-AUC de 0.858 a 0.862, sin aumentar la brecha train-test. Modelo final desplegado con interfaz en Streamlit.</t>
-        </is>
-      </c>
-      <c r="H4" s="24" t="inlineStr">
-        <is>
-          <t>No aplica — el proyecto se desarrolló íntegramente en Python, según lo solicitado por la profesora.</t>
-        </is>
-      </c>
+    <row r="4" spans="1:14" ht="220.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="G4" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="H4" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -792,6 +784,6 @@
     <mergeCell ref="L2:L3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
--- a/entregables/Proyectos_2026-2_resumen.xlsx
+++ b/entregables/Proyectos_2026-2_resumen.xlsx
@@ -1,166 +1,64 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d2f440db51dfc7c7/Documentos/GitHub/Mineria-de-Datos-en-Phyton/entregables/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_1B376543467C3BD86F56B4FF9C1B6216DD652D8C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C9390522-C76D-4C35-AB4B-7317722291F9}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hoja1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="191028" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
-  <si>
-    <t>Equipo</t>
-  </si>
-  <si>
-    <t>Empresa 
-(a quien pertenecen los datos)</t>
-  </si>
-  <si>
-    <t>Datos Iniciales
-(cantidad de columnas, cantidad de filas, variable objetivo)</t>
-  </si>
-  <si>
-    <t>Enlace para descarga de los datos</t>
-  </si>
-  <si>
-    <t>MINERÍA DE DATOS</t>
-  </si>
-  <si>
-    <t>VISUALIZACIÓN</t>
-  </si>
-  <si>
-    <t>BODEGA DE DATOS</t>
-  </si>
-  <si>
-    <t>ETL</t>
-  </si>
-  <si>
-    <t>BIG DATA</t>
-  </si>
-  <si>
-    <t>CONCLUSIÓN FINAL</t>
-  </si>
-  <si>
-    <t>Calidad  de datos</t>
-  </si>
-  <si>
-    <t>Preparación de datos</t>
-  </si>
-  <si>
-    <t>Modelos analíticos Python</t>
-  </si>
-  <si>
-    <t>Modelos analíticos Knime</t>
-  </si>
-  <si>
-    <t>Enlace al power BI y una conclusión de los gráficos</t>
-  </si>
-  <si>
-    <t>Hechos</t>
-  </si>
-  <si>
-    <t>Dimensiones</t>
-  </si>
-  <si>
-    <t>Extraccion - Transformacion - Carga</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> (enlaces de los dashboards)</t>
-  </si>
-  <si>
-    <t>Diagnóstico de las dimensiones de calidad</t>
-  </si>
-  <si>
-    <t>Indicar los pasos de preparación implementados y hallazgos</t>
-  </si>
-  <si>
-    <t>(Indicar resultados de modelos predictivos con validación cruzada)</t>
-  </si>
-  <si>
-    <t>(Indicar modelos creados y una conclusion de cada modelo)</t>
-  </si>
-  <si>
-    <t>Nicolás Castrillón, Mateo Roldán, Matías Arango</t>
-  </si>
-  <si>
-    <t>No aplica — dataset histórico público (pasajeros del RMS Titanic), sin empresa propietaria</t>
-  </si>
-  <si>
-    <t>12 columnas originales (7 usadas como predictoras tras la selección de factores), 891 filas, variable objetivo: Survived (1 = sobrevivió, 0 = no sobrevivió)</t>
-  </si>
-  <si>
-    <t>https://github.com/Mateo-R99/Mineria-de-Datos-en-Phyton/blob/main/data/titanic.csv</t>
-  </si>
-  <si>
-    <t>Completitud: Age con 19.8% de nulos (177/891, imputados con la mediana), Embarked con 0.2% de nulos (2/891, imputados con la moda), Cabin con 77% de nulos (687/891, se descartó la columna por no ser confiablemente imputable). Duplicidad: 0 filas duplicadas. Exactitud: sin edades ni tarifas fuera de rango (no se encontraron valores negativos ni edades &gt;100). Conformidad: formatos de las variables consistentes en todo el archivo. Integridad: dataset autocontenido, no requiere cruces con otras fuentes.</t>
-  </si>
-  <si>
-    <t>Se eliminaron PassengerId, Name y Ticket (identificadores sin valor predictivo) y Cabin (77% nula). Imputación de Age (mediana) y Embarked (moda), escalado estandarizado de variables numéricas y codificación dummy de categóricas, todo dentro de un Pipeline de scikit-learn ajustado solo con el conjunto de entrenamiento (evita fuga de información). Selección de factores con correlación punto-biserial, chi-cuadrado + V de Cramér e importancia de Random Forest: Sex (V=0.54) y Pclass (V=0.34) resultaron las variables más asociadas a la supervivencia, seguidas de Fare (r=0.26) y Age (relación no lineal, relevante en el Random Forest pese a correlación lineal débil). Sin redundancia fuerte entre predictoras (correlación máxima entre ellas: 0.41).</t>
-  </si>
-  <si>
-    <t>6 modelos evaluados con validación cruzada estratificada de 5 folds (accuracy / CV, brecha train-test): Árbol de Decisión 0.801 (brecha 0.070), KNN 0.775 (la más baja), Red Neuronal (MLP) 0.808 (brecha 0.060), SVM 0.825 (brecha 0.026, buena generalización), Random Forest 0.822 (mejor ROC-AUC: 0.868, brecha 0.060), XGBoost 0.825 (brecha 0.127, overfitting claro). Se optimizó Random Forest con GridSearchCV (n_estimators=200, max_depth=6, min_samples_leaf=1, max_features='sqrt'): ROC-AUC de validación cruzada subió de 0.868 a 0.871, y en el conjunto de prueba (no usado durante la búsqueda) el accuracy pasó de 0.813 a 0.817 y el ROC-AUC de 0.858 a 0.862, sin aumentar la brecha train-test. Modelo final desplegado con interfaz en Streamlit.</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="5">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color rgb="FF000000"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="10"/>
+      <sz val="11"/>
+      <u val="single"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="8">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -173,19 +71,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
+        <fgColor theme="9" tint="0.5999938962981048"/>
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
+        <fgColor theme="5" tint="0.5999938962981048"/>
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.39997558519241921"/>
+        <fgColor theme="4" tint="0.3999755851924192"/>
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
@@ -197,12 +95,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <fgColor theme="2" tint="-0.09997863704336681"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -239,6 +137,19 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -260,6 +171,35 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -291,81 +231,79 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="25">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Hyperlink" xfId="1"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors/>
 </styleSheet>
 </file>
 
@@ -631,142 +569,231 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:N4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="14.77734375" customWidth="1"/>
-    <col min="2" max="2" width="45.21875" customWidth="1"/>
-    <col min="3" max="3" width="57" customWidth="1"/>
-    <col min="4" max="5" width="93.21875" customWidth="1"/>
-    <col min="6" max="6" width="86" customWidth="1"/>
-    <col min="7" max="7" width="83" customWidth="1"/>
-    <col min="8" max="8" width="89.77734375" customWidth="1"/>
-    <col min="9" max="9" width="159" customWidth="1"/>
-    <col min="10" max="10" width="64.21875" customWidth="1"/>
-    <col min="11" max="11" width="80.77734375" customWidth="1"/>
-    <col min="12" max="12" width="89" customWidth="1"/>
-    <col min="13" max="13" width="77.44140625" customWidth="1"/>
-    <col min="14" max="14" width="81.44140625" customWidth="1"/>
+    <col width="14.81640625" customWidth="1" min="1" max="1"/>
+    <col width="45.1796875" customWidth="1" min="2" max="2"/>
+    <col width="57" customWidth="1" min="3" max="3"/>
+    <col width="93.1796875" customWidth="1" min="4" max="5"/>
+    <col width="86" customWidth="1" min="6" max="6"/>
+    <col width="83" customWidth="1" min="7" max="7"/>
+    <col width="89.81640625" customWidth="1" min="8" max="8"/>
+    <col width="159" customWidth="1" min="9" max="9"/>
+    <col width="64.26953125" customWidth="1" min="10" max="10"/>
+    <col width="80.7265625" customWidth="1" min="11" max="11"/>
+    <col width="89" customWidth="1" min="12" max="12"/>
+    <col width="77.453125" customWidth="1" min="13" max="13"/>
+    <col width="81.453125" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="J1" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="K1" s="17"/>
-      <c r="L1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N1" s="4" t="s">
-        <v>9</v>
+    <row r="1" ht="15" customHeight="1">
+      <c r="A1" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
+      <c r="B1" s="15" t="inlineStr">
+        <is>
+          <t>Empresa 
+(a quien pertenecen los datos)</t>
+        </is>
+      </c>
+      <c r="C1" s="15" t="inlineStr">
+        <is>
+          <t>Datos Iniciales
+(cantidad de columnas, cantidad de filas, variable objetivo)</t>
+        </is>
+      </c>
+      <c r="D1" s="15" t="inlineStr">
+        <is>
+          <t>Enlace para descarga de los datos</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>MINERÍA DE DATOS</t>
+        </is>
+      </c>
+      <c r="F1" s="20" t="n"/>
+      <c r="G1" s="20" t="n"/>
+      <c r="H1" s="21" t="n"/>
+      <c r="I1" s="9" t="inlineStr">
+        <is>
+          <t>VISUALIZACIÓN</t>
+        </is>
+      </c>
+      <c r="J1" s="10" t="inlineStr">
+        <is>
+          <t>BODEGA DE DATOS</t>
+        </is>
+      </c>
+      <c r="K1" s="21" t="n"/>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t>ETL</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
+          <t>BIG DATA</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>CONCLUSIÓN FINAL</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="12"/>
-      <c r="B2" s="12"/>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I2" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="J2" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="K2" s="16" t="s">
-        <v>16</v>
-      </c>
-      <c r="L2" s="22" t="s">
-        <v>17</v>
-      </c>
-      <c r="M2" s="18" t="s">
-        <v>18</v>
-      </c>
-      <c r="N2" s="15"/>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="22" t="n"/>
+      <c r="B2" s="22" t="n"/>
+      <c r="C2" s="22" t="n"/>
+      <c r="D2" s="22" t="n"/>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>Calidad  de datos</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>Preparación de datos</t>
+        </is>
+      </c>
+      <c r="G2" s="1" t="inlineStr">
+        <is>
+          <t>Modelos analíticos Python</t>
+        </is>
+      </c>
+      <c r="H2" s="1" t="inlineStr">
+        <is>
+          <t>Modelos analíticos Knime</t>
+        </is>
+      </c>
+      <c r="I2" s="11" t="inlineStr">
+        <is>
+          <t>Enlace al power BI y una conclusión de los gráficos</t>
+        </is>
+      </c>
+      <c r="J2" s="10" t="inlineStr">
+        <is>
+          <t>Hechos</t>
+        </is>
+      </c>
+      <c r="K2" s="10" t="inlineStr">
+        <is>
+          <t>Dimensiones</t>
+        </is>
+      </c>
+      <c r="L2" s="16" t="inlineStr">
+        <is>
+          <t>Extraccion - Transformacion - Carga</t>
+        </is>
+      </c>
+      <c r="M2" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> (enlaces de los dashboards)</t>
+        </is>
+      </c>
+      <c r="N2" s="13" t="n"/>
     </row>
-    <row r="3" spans="1:14" ht="29.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="13"/>
-      <c r="B3" s="13"/>
-      <c r="C3" s="13"/>
-      <c r="D3" s="13"/>
-      <c r="E3" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="H3" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="I3" s="13"/>
-      <c r="J3" s="13"/>
-      <c r="K3" s="13"/>
-      <c r="L3" s="13"/>
-      <c r="M3" s="13"/>
-      <c r="N3" s="13"/>
+    <row r="3" ht="29.15" customHeight="1">
+      <c r="A3" s="23" t="n"/>
+      <c r="B3" s="23" t="n"/>
+      <c r="C3" s="23" t="n"/>
+      <c r="D3" s="23" t="n"/>
+      <c r="E3" s="8" t="inlineStr">
+        <is>
+          <t>Diagnóstico de las dimensiones de calidad</t>
+        </is>
+      </c>
+      <c r="F3" s="8" t="inlineStr">
+        <is>
+          <t>Indicar los pasos de preparación implementados y hallazgos</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="inlineStr">
+        <is>
+          <t>(Indicar resultados de modelos predictivos con validación cruzada)</t>
+        </is>
+      </c>
+      <c r="H3" s="7" t="inlineStr">
+        <is>
+          <t>(Indicar modelos creados y una conclusion de cada modelo)</t>
+        </is>
+      </c>
+      <c r="I3" s="23" t="n"/>
+      <c r="J3" s="23" t="n"/>
+      <c r="K3" s="23" t="n"/>
+      <c r="L3" s="23" t="n"/>
+      <c r="M3" s="23" t="n"/>
+      <c r="N3" s="23" t="n"/>
     </row>
-    <row r="4" spans="1:14" ht="220.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="F4" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="G4" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="H4" s="10"/>
+    <row r="4" ht="340" customHeight="1">
+      <c r="A4" s="24" t="inlineStr">
+        <is>
+          <t>Nicolás Castrillón, Mateo Roldán, Matías Arango</t>
+        </is>
+      </c>
+      <c r="B4" s="24" t="inlineStr">
+        <is>
+          <t>No aplica — dataset histórico público (pasajeros del RMS Titanic), sin empresa propietaria</t>
+        </is>
+      </c>
+      <c r="C4" s="24" t="inlineStr">
+        <is>
+          <t>12 columnas originales (7 usadas como predictoras tras la selección de factores), 891 filas, variable objetivo: Survived (1 = sobrevivió, 0 = no sobrevivió)</t>
+        </is>
+      </c>
+      <c r="D4" s="24" t="inlineStr">
+        <is>
+          <t>https://github.com/Mateo-R99/Mineria-de-Datos-en-Phyton/blob/main/data/titanic.csv</t>
+        </is>
+      </c>
+      <c r="E4" s="24" t="inlineStr">
+        <is>
+          <t>Diagnóstico por dimensión de calidad:
+- Completitud: Age con 19.8% de nulos (177/891, imputados con la mediana); Embarked con 0.2% de nulos (2/891, imputados con la moda); Cabin con 77% de nulos (687/891, se descartó por no ser confiablemente imputable).
+- Duplicidad: 0 filas duplicadas.
+- Exactitud: sin edades ni tarifas fuera de rango (no se encontraron valores negativos ni edades mayores a 100 años).
+- Conformidad: formatos de las variables consistentes en todo el archivo.
+- Integridad: dataset autocontenido, no requiere cruces con otras fuentes.</t>
+        </is>
+      </c>
+      <c r="F4" s="24" t="inlineStr">
+        <is>
+          <t>1. Limpieza: se eliminaron PassengerId, Name y Ticket (identificadores sin valor predictivo) y Cabin (77% nula).
+2. Imputación: Age con la mediana, Embarked con la moda.
+3. Transformación: escalado estandarizado de las variables numéricas y codificación dummy de las categóricas, todo dentro de un Pipeline de scikit-learn ajustado solo con el conjunto de entrenamiento (evita fuga de información).
+4. Selección de factores (correlación punto-biserial, chi-cuadrado + V de Cramér, importancia de Random Forest): Sex (V=0.54) y Pclass (V=0.34) son las variables más asociadas a la supervivencia, seguidas de Fare (r=0.26) y Age (relación no lineal, relevante en el Random Forest pese a su correlación lineal débil).
+Hallazgo: sin redundancia fuerte entre predictoras (correlación máxima entre ellas: 0.41).</t>
+        </is>
+      </c>
+      <c r="G4" s="24" t="inlineStr">
+        <is>
+          <t>6 modelos evaluados con validación cruzada estratificada de 5 folds (accuracy / CV, brecha train-test):
+- Árbol de Decisión: 0.801 (brecha 0.070). Mayor variabilidad entre folds (±0.053), más inestable que los modelos de ensamble.
+- KNN: 0.775, el más bajo de los seis. Cierto underfitting relativo frente a los modelos basados en árboles.
+- Red Neuronal (MLP): 0.808 (brecha 0.060). Desempeño intermedio, sin overfitting severo.
+- SVM: 0.825 (brecha 0.026). La mejor generalización del grupo.
+- Random Forest: 0.822, mejor ROC-AUC de los seis (0.868), brecha moderada (0.060).
+- XGBoost: 0.825 (empata con SVM) pero brecha 0.127 — el caso más claro de overfitting.
+Conclusión: ningún modelo supera ~0.87 de ROC-AUC, lo que sugiere un techo de desempeño limitado por el tamaño del dataset (891 filas) más que por el algoritmo.
+Se optimizó Random Forest con GridSearchCV (n_estimators=200, max_depth=6, min_samples_leaf=1, max_features='sqrt'; 72 combinaciones x 5 folds = 360 ajustes): el ROC-AUC de validación cruzada subió de 0.868 a 0.871, y en el conjunto de prueba (no usado durante la búsqueda) el accuracy pasó de 0.813 a 0.817 y el ROC-AUC de 0.858 a 0.862, sin aumentar la brecha train-test (≈0.058-0.060).
+Modelo final desplegado con interfaz gráfica en Streamlit (ejecución local; ver instrucciones en el repositorio).
+Repositorio: https://github.com/Mateo-R99/Mineria-de-Datos-en-Phyton</t>
+        </is>
+      </c>
+      <c r="H4" s="24" t="inlineStr">
+        <is>
+          <t>No aplica — el proyecto se desarrolló íntegramente en Python, según lo solicitado por la profesora.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -784,6 +811,6 @@
     <mergeCell ref="L2:L3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
--- a/entregables/Proyectos_2026-2_resumen.xlsx
+++ b/entregables/Proyectos_2026-2_resumen.xlsx
@@ -1,64 +1,185 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d2f440db51dfc7c7/Documentos/GitHub/Mineria-de-Datos-en-Phyton/entregables/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_3A286543E024BDF90357B4FF9C1B62164DE956AE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CC79E26F-E0EB-47D0-A880-CF9AE8306548}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hoja1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="191028" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+  <si>
+    <t>Equipo</t>
+  </si>
+  <si>
+    <t>Empresa 
+(a quien pertenecen los datos)</t>
+  </si>
+  <si>
+    <t>Datos Iniciales
+(cantidad de columnas, cantidad de filas, variable objetivo)</t>
+  </si>
+  <si>
+    <t>Enlace para descarga de los datos</t>
+  </si>
+  <si>
+    <t>MINERÍA DE DATOS</t>
+  </si>
+  <si>
+    <t>VISUALIZACIÓN</t>
+  </si>
+  <si>
+    <t>BODEGA DE DATOS</t>
+  </si>
+  <si>
+    <t>ETL</t>
+  </si>
+  <si>
+    <t>BIG DATA</t>
+  </si>
+  <si>
+    <t>CONCLUSIÓN FINAL</t>
+  </si>
+  <si>
+    <t>Calidad  de datos</t>
+  </si>
+  <si>
+    <t>Preparación de datos</t>
+  </si>
+  <si>
+    <t>Modelos analíticos Python</t>
+  </si>
+  <si>
+    <t>Modelos analíticos Knime</t>
+  </si>
+  <si>
+    <t>Enlace al power BI y una conclusión de los gráficos</t>
+  </si>
+  <si>
+    <t>Hechos</t>
+  </si>
+  <si>
+    <t>Dimensiones</t>
+  </si>
+  <si>
+    <t>Extraccion - Transformacion - Carga</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> (enlaces de los dashboards)</t>
+  </si>
+  <si>
+    <t>Diagnóstico de las dimensiones de calidad</t>
+  </si>
+  <si>
+    <t>Indicar los pasos de preparación implementados y hallazgos</t>
+  </si>
+  <si>
+    <t>(Indicar resultados de modelos predictivos con validación cruzada)</t>
+  </si>
+  <si>
+    <t>(Indicar modelos creados y una conclusion de cada modelo)</t>
+  </si>
+  <si>
+    <t>Nicolás Castrillón, Mateo Roldán, Matías Arango</t>
+  </si>
+  <si>
+    <t>No aplica — dataset histórico público (pasajeros del RMS Titanic), sin empresa propietaria</t>
+  </si>
+  <si>
+    <t>12 columnas originales (7 usadas como predictoras tras la selección de factores), 891 filas, variable objetivo: Survived (1 = sobrevivió, 0 = no sobrevivió)</t>
+  </si>
+  <si>
+    <t>https://github.com/Mateo-R99/Mineria-de-Datos-en-Phyton/blob/main/data/titanic.csv</t>
+  </si>
+  <si>
+    <t>Diagnóstico por dimensión de calidad:
+- Completitud: Age con 19.8% de nulos (177/891, imputados con la mediana); Embarked con 0.2% de nulos (2/891, imputados con la moda); Cabin con 77% de nulos (687/891, se descartó por no ser confiablemente imputable).
+- Duplicidad: 0 filas duplicadas.
+- Exactitud: sin edades ni tarifas fuera de rango (no se encontraron valores negativos ni edades mayores a 100 años).
+- Conformidad: formatos de las variables consistentes en todo el archivo.
+- Integridad: dataset autocontenido, no requiere cruces con otras fuentes.</t>
+  </si>
+  <si>
+    <t>1. Limpieza: se eliminaron PassengerId, Name y Ticket (identificadores sin valor predictivo) y Cabin (77% nula).
+2. Imputación: Age con la mediana, Embarked con la moda.
+3. Transformación: escalado estandarizado de las variables numéricas y codificación dummy de las categóricas, todo dentro de un Pipeline de scikit-learn ajustado solo con el conjunto de entrenamiento (evita fuga de información).
+4. Selección de factores (correlación punto-biserial, chi-cuadrado + V de Cramér, importancia de Random Forest): Sex (V=0.54) y Pclass (V=0.34) son las variables más asociadas a la supervivencia, seguidas de Fare (r=0.26) y Age (relación no lineal, relevante en el Random Forest pese a su correlación lineal débil).
+Hallazgo: sin redundancia fuerte entre predictoras (correlación máxima entre ellas: 0.41).</t>
+  </si>
+  <si>
+    <t>6 modelos evaluados con validación cruzada estratificada de 5 folds (accuracy / CV, brecha train-test):
+- Árbol de Decisión: 0.801 (brecha 0.070). Mayor variabilidad entre folds (±0.053), más inestable que los modelos de ensamble.
+- KNN: 0.775, el más bajo de los seis. Cierto underfitting relativo frente a los modelos basados en árboles.
+- Red Neuronal (MLP): 0.808 (brecha 0.060). Desempeño intermedio, sin overfitting severo.
+- SVM: 0.825 (brecha 0.026). La mejor generalización del grupo.
+- Random Forest: 0.822, mejor ROC-AUC de los seis (0.868), brecha moderada (0.060).
+- XGBoost: 0.825 (empata con SVM) pero brecha 0.127 — el caso más claro de overfitting.
+Conclusión: ningún modelo supera ~0.87 de ROC-AUC, lo que sugiere un techo de desempeño limitado por el tamaño del dataset (891 filas) más que por el algoritmo.
+Se optimizó Random Forest con GridSearchCV (n_estimators=200, max_depth=6, min_samples_leaf=1, max_features='sqrt'; 72 combinaciones x 5 folds = 360 ajustes): el ROC-AUC de validación cruzada subió de 0.868 a 0.871, y en el conjunto de prueba (no usado durante la búsqueda) el accuracy pasó de 0.813 a 0.817 y el ROC-AUC de 0.858 a 0.862, sin aumentar la brecha train-test (≈0.058-0.060).
+Modelo final desplegado con interfaz gráfica en Streamlit (ejecución local; ver instrucciones en el repositorio).
+Repositorio: https://github.com/Mateo-R99/Mineria-de-Datos-en-Phyton</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="5">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b val="1"/>
-      <color rgb="FF000000"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color rgb="FF000000"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="10"/>
-      <sz val="11"/>
-      <u val="single"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b val="1"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="8">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -71,19 +192,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.5999938962981048"/>
+        <fgColor theme="9" tint="0.59999389629810485"/>
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.5999938962981048"/>
+        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.3999755851924192"/>
+        <fgColor theme="4" tint="0.39997558519241921"/>
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
@@ -95,12 +216,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="2" tint="-0.09997863704336681"/>
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -137,19 +258,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -171,35 +279,6 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -231,79 +310,81 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="23">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Hyperlink" xfId="1"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -569,231 +650,142 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col width="14.81640625" customWidth="1" min="1" max="1"/>
-    <col width="45.1796875" customWidth="1" min="2" max="2"/>
-    <col width="57" customWidth="1" min="3" max="3"/>
-    <col width="93.1796875" customWidth="1" min="4" max="5"/>
-    <col width="86" customWidth="1" min="6" max="6"/>
-    <col width="83" customWidth="1" min="7" max="7"/>
-    <col width="89.81640625" customWidth="1" min="8" max="8"/>
-    <col width="159" customWidth="1" min="9" max="9"/>
-    <col width="64.26953125" customWidth="1" min="10" max="10"/>
-    <col width="80.7265625" customWidth="1" min="11" max="11"/>
-    <col width="89" customWidth="1" min="12" max="12"/>
-    <col width="77.453125" customWidth="1" min="13" max="13"/>
-    <col width="81.453125" customWidth="1" min="14" max="14"/>
+    <col min="1" max="1" width="14.77734375" customWidth="1"/>
+    <col min="2" max="2" width="45.21875" customWidth="1"/>
+    <col min="3" max="3" width="57" customWidth="1"/>
+    <col min="4" max="5" width="93.21875" customWidth="1"/>
+    <col min="6" max="6" width="86" customWidth="1"/>
+    <col min="7" max="7" width="83" customWidth="1"/>
+    <col min="8" max="8" width="89.77734375" customWidth="1"/>
+    <col min="9" max="9" width="159" customWidth="1"/>
+    <col min="10" max="10" width="64.21875" customWidth="1"/>
+    <col min="11" max="11" width="80.77734375" customWidth="1"/>
+    <col min="12" max="12" width="89" customWidth="1"/>
+    <col min="13" max="13" width="77.44140625" customWidth="1"/>
+    <col min="14" max="14" width="81.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1">
-      <c r="A1" s="14" t="inlineStr">
-        <is>
-          <t>Equipo</t>
-        </is>
-      </c>
-      <c r="B1" s="15" t="inlineStr">
-        <is>
-          <t>Empresa 
-(a quien pertenecen los datos)</t>
-        </is>
-      </c>
-      <c r="C1" s="15" t="inlineStr">
-        <is>
-          <t>Datos Iniciales
-(cantidad de columnas, cantidad de filas, variable objetivo)</t>
-        </is>
-      </c>
-      <c r="D1" s="15" t="inlineStr">
-        <is>
-          <t>Enlace para descarga de los datos</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>MINERÍA DE DATOS</t>
-        </is>
-      </c>
-      <c r="F1" s="20" t="n"/>
-      <c r="G1" s="20" t="n"/>
-      <c r="H1" s="21" t="n"/>
-      <c r="I1" s="9" t="inlineStr">
-        <is>
-          <t>VISUALIZACIÓN</t>
-        </is>
-      </c>
-      <c r="J1" s="10" t="inlineStr">
-        <is>
-          <t>BODEGA DE DATOS</t>
-        </is>
-      </c>
-      <c r="K1" s="21" t="n"/>
-      <c r="L1" s="2" t="inlineStr">
-        <is>
-          <t>ETL</t>
-        </is>
-      </c>
-      <c r="M1" s="3" t="inlineStr">
-        <is>
-          <t>BIG DATA</t>
-        </is>
-      </c>
-      <c r="N1" s="4" t="inlineStr">
-        <is>
-          <t>CONCLUSIÓN FINAL</t>
-        </is>
+    <row r="1" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="17"/>
+      <c r="L1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="22" t="n"/>
-      <c r="B2" s="22" t="n"/>
-      <c r="C2" s="22" t="n"/>
-      <c r="D2" s="22" t="n"/>
-      <c r="E2" s="5" t="inlineStr">
-        <is>
-          <t>Calidad  de datos</t>
-        </is>
-      </c>
-      <c r="F2" s="5" t="inlineStr">
-        <is>
-          <t>Preparación de datos</t>
-        </is>
-      </c>
-      <c r="G2" s="1" t="inlineStr">
-        <is>
-          <t>Modelos analíticos Python</t>
-        </is>
-      </c>
-      <c r="H2" s="1" t="inlineStr">
-        <is>
-          <t>Modelos analíticos Knime</t>
-        </is>
-      </c>
-      <c r="I2" s="11" t="inlineStr">
-        <is>
-          <t>Enlace al power BI y una conclusión de los gráficos</t>
-        </is>
-      </c>
-      <c r="J2" s="10" t="inlineStr">
-        <is>
-          <t>Hechos</t>
-        </is>
-      </c>
-      <c r="K2" s="10" t="inlineStr">
-        <is>
-          <t>Dimensiones</t>
-        </is>
-      </c>
-      <c r="L2" s="16" t="inlineStr">
-        <is>
-          <t>Extraccion - Transformacion - Carga</t>
-        </is>
-      </c>
-      <c r="M2" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> (enlaces de los dashboards)</t>
-        </is>
-      </c>
-      <c r="N2" s="13" t="n"/>
+    <row r="2" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="12"/>
+      <c r="B2" s="12"/>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2" s="21" t="s">
+        <v>14</v>
+      </c>
+      <c r="J2" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="K2" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="L2" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="M2" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="N2" s="15"/>
     </row>
-    <row r="3" ht="29.15" customHeight="1">
-      <c r="A3" s="23" t="n"/>
-      <c r="B3" s="23" t="n"/>
-      <c r="C3" s="23" t="n"/>
-      <c r="D3" s="23" t="n"/>
-      <c r="E3" s="8" t="inlineStr">
-        <is>
-          <t>Diagnóstico de las dimensiones de calidad</t>
-        </is>
-      </c>
-      <c r="F3" s="8" t="inlineStr">
-        <is>
-          <t>Indicar los pasos de preparación implementados y hallazgos</t>
-        </is>
-      </c>
-      <c r="G3" s="6" t="inlineStr">
-        <is>
-          <t>(Indicar resultados de modelos predictivos con validación cruzada)</t>
-        </is>
-      </c>
-      <c r="H3" s="7" t="inlineStr">
-        <is>
-          <t>(Indicar modelos creados y una conclusion de cada modelo)</t>
-        </is>
-      </c>
-      <c r="I3" s="23" t="n"/>
-      <c r="J3" s="23" t="n"/>
-      <c r="K3" s="23" t="n"/>
-      <c r="L3" s="23" t="n"/>
-      <c r="M3" s="23" t="n"/>
-      <c r="N3" s="23" t="n"/>
+    <row r="3" spans="1:14" ht="29.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="13"/>
+      <c r="B3" s="13"/>
+      <c r="C3" s="13"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I3" s="13"/>
+      <c r="J3" s="13"/>
+      <c r="K3" s="13"/>
+      <c r="L3" s="13"/>
+      <c r="M3" s="13"/>
+      <c r="N3" s="13"/>
     </row>
-    <row r="4" ht="340" customHeight="1">
-      <c r="A4" s="24" t="inlineStr">
-        <is>
-          <t>Nicolás Castrillón, Mateo Roldán, Matías Arango</t>
-        </is>
-      </c>
-      <c r="B4" s="24" t="inlineStr">
-        <is>
-          <t>No aplica — dataset histórico público (pasajeros del RMS Titanic), sin empresa propietaria</t>
-        </is>
-      </c>
-      <c r="C4" s="24" t="inlineStr">
-        <is>
-          <t>12 columnas originales (7 usadas como predictoras tras la selección de factores), 891 filas, variable objetivo: Survived (1 = sobrevivió, 0 = no sobrevivió)</t>
-        </is>
-      </c>
-      <c r="D4" s="24" t="inlineStr">
-        <is>
-          <t>https://github.com/Mateo-R99/Mineria-de-Datos-en-Phyton/blob/main/data/titanic.csv</t>
-        </is>
-      </c>
-      <c r="E4" s="24" t="inlineStr">
-        <is>
-          <t>Diagnóstico por dimensión de calidad:
-- Completitud: Age con 19.8% de nulos (177/891, imputados con la mediana); Embarked con 0.2% de nulos (2/891, imputados con la moda); Cabin con 77% de nulos (687/891, se descartó por no ser confiablemente imputable).
-- Duplicidad: 0 filas duplicadas.
-- Exactitud: sin edades ni tarifas fuera de rango (no se encontraron valores negativos ni edades mayores a 100 años).
-- Conformidad: formatos de las variables consistentes en todo el archivo.
-- Integridad: dataset autocontenido, no requiere cruces con otras fuentes.</t>
-        </is>
-      </c>
-      <c r="F4" s="24" t="inlineStr">
-        <is>
-          <t>1. Limpieza: se eliminaron PassengerId, Name y Ticket (identificadores sin valor predictivo) y Cabin (77% nula).
-2. Imputación: Age con la mediana, Embarked con la moda.
-3. Transformación: escalado estandarizado de las variables numéricas y codificación dummy de las categóricas, todo dentro de un Pipeline de scikit-learn ajustado solo con el conjunto de entrenamiento (evita fuga de información).
-4. Selección de factores (correlación punto-biserial, chi-cuadrado + V de Cramér, importancia de Random Forest): Sex (V=0.54) y Pclass (V=0.34) son las variables más asociadas a la supervivencia, seguidas de Fare (r=0.26) y Age (relación no lineal, relevante en el Random Forest pese a su correlación lineal débil).
-Hallazgo: sin redundancia fuerte entre predictoras (correlación máxima entre ellas: 0.41).</t>
-        </is>
-      </c>
-      <c r="G4" s="24" t="inlineStr">
-        <is>
-          <t>6 modelos evaluados con validación cruzada estratificada de 5 folds (accuracy / CV, brecha train-test):
-- Árbol de Decisión: 0.801 (brecha 0.070). Mayor variabilidad entre folds (±0.053), más inestable que los modelos de ensamble.
-- KNN: 0.775, el más bajo de los seis. Cierto underfitting relativo frente a los modelos basados en árboles.
-- Red Neuronal (MLP): 0.808 (brecha 0.060). Desempeño intermedio, sin overfitting severo.
-- SVM: 0.825 (brecha 0.026). La mejor generalización del grupo.
-- Random Forest: 0.822, mejor ROC-AUC de los seis (0.868), brecha moderada (0.060).
-- XGBoost: 0.825 (empata con SVM) pero brecha 0.127 — el caso más claro de overfitting.
-Conclusión: ningún modelo supera ~0.87 de ROC-AUC, lo que sugiere un techo de desempeño limitado por el tamaño del dataset (891 filas) más que por el algoritmo.
-Se optimizó Random Forest con GridSearchCV (n_estimators=200, max_depth=6, min_samples_leaf=1, max_features='sqrt'; 72 combinaciones x 5 folds = 360 ajustes): el ROC-AUC de validación cruzada subió de 0.868 a 0.871, y en el conjunto de prueba (no usado durante la búsqueda) el accuracy pasó de 0.813 a 0.817 y el ROC-AUC de 0.858 a 0.862, sin aumentar la brecha train-test (≈0.058-0.060).
-Modelo final desplegado con interfaz gráfica en Streamlit (ejecución local; ver instrucciones en el repositorio).
-Repositorio: https://github.com/Mateo-R99/Mineria-de-Datos-en-Phyton</t>
-        </is>
-      </c>
-      <c r="H4" s="24" t="inlineStr">
-        <is>
-          <t>No aplica — el proyecto se desarrolló íntegramente en Python, según lo solicitado por la profesora.</t>
-        </is>
-      </c>
+    <row r="4" spans="1:14" ht="340.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="G4" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="H4" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -811,6 +803,6 @@
     <mergeCell ref="L2:L3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>